--- a/data/Diessenhofen/cost/total_demand.xlsx
+++ b/data/Diessenhofen/cost/total_demand.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>219988.9288378455</v>
+        <v>9166.205368243562</v>
       </c>
     </row>
     <row r="3">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>115412.2416345276</v>
+        <v>4808.84340143865</v>
       </c>
     </row>
     <row r="4">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>648578.3838642666</v>
+        <v>27024.09932767777</v>
       </c>
     </row>
   </sheetData>
